--- a/Output/AllModels_SensitivityExchangeProcesses_12000.xlsx
+++ b/Output/AllModels_SensitivityExchangeProcesses_12000.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">[28.75, 40.22]</t>
   </si>
   <si>
-    <t xml:space="preserve">111.11***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[100.32, 123.32]</t>
+    <t xml:space="preserve">111.13***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[100.39, 123.07]</t>
   </si>
   <si>
     <t xml:space="preserve">3.68***</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">0.97</t>
   </si>
   <si>
-    <t xml:space="preserve">[  0.92,   1.04]</t>
+    <t xml:space="preserve">[  0.91,   1.04]</t>
   </si>
   <si>
     <t xml:space="preserve">[-0.12, 0.09]</t>
@@ -287,9 +287,6 @@
     <t xml:space="preserve">[ 0.87,  1.10]</t>
   </si>
   <si>
-    <t xml:space="preserve">[  0.91,   1.04]</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.26***</t>
   </si>
   <si>
@@ -452,13 +449,13 @@
     <t xml:space="preserve">[ 0.64,  1.35]</t>
   </si>
   <si>
-    <t xml:space="preserve">[  0.77,   1.56]</t>
+    <t xml:space="preserve">[  0.76,   1.55]</t>
   </si>
   <si>
     <t xml:space="preserve">0.26</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.50, 1.01]</t>
+    <t xml:space="preserve">[-0.49, 1.00]</t>
   </si>
   <si>
     <t xml:space="preserve">2.79</t>
@@ -485,7 +482,7 @@
     <t xml:space="preserve">0.35</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.40, 1.09]</t>
+    <t xml:space="preserve">[-0.40, 1.11]</t>
   </si>
   <si>
     <t xml:space="preserve">2.55</t>
@@ -509,13 +506,13 @@
     <t xml:space="preserve">[ 0.32,  1.80]</t>
   </si>
   <si>
-    <t xml:space="preserve">[  0.61,   1.59]</t>
+    <t xml:space="preserve">[  0.61,   1.58]</t>
   </si>
   <si>
     <t xml:space="preserve">-0.32</t>
   </si>
   <si>
-    <t xml:space="preserve">[-1.29, 0.64]</t>
+    <t xml:space="preserve">[-1.27, 0.64]</t>
   </si>
   <si>
     <t xml:space="preserve">25.64</t>
@@ -539,13 +536,13 @@
     <t xml:space="preserve">[ 0.23,  1.35]</t>
   </si>
   <si>
-    <t xml:space="preserve">[  0.61,   1.52]</t>
+    <t xml:space="preserve">[  0.61,   1.51]</t>
   </si>
   <si>
     <t xml:space="preserve">-0.33</t>
   </si>
   <si>
-    <t xml:space="preserve">[-1.28, 0.61]</t>
+    <t xml:space="preserve">[-1.30, 0.62]</t>
   </si>
   <si>
     <t xml:space="preserve">2.88</t>
@@ -569,13 +566,13 @@
     <t xml:space="preserve">[ 0.73,  2.84]</t>
   </si>
   <si>
-    <t xml:space="preserve">[  0.51,   1.59]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.93, 1.43]</t>
+    <t xml:space="preserve">[  0.51,   1.58]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.94, 1.40]</t>
   </si>
   <si>
     <t xml:space="preserve">1.65</t>
@@ -608,7 +605,7 @@
     <t xml:space="preserve">0.12</t>
   </si>
   <si>
-    <t xml:space="preserve">[-1.07, 1.29]</t>
+    <t xml:space="preserve">[-1.05, 1.29]</t>
   </si>
   <si>
     <t xml:space="preserve">[0.00,    1.73]</t>
@@ -635,7 +632,7 @@
     <t xml:space="preserve">0.15</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.14, 0.44]</t>
+    <t xml:space="preserve">[-0.13, 0.44]</t>
   </si>
   <si>
     <t xml:space="preserve">0.57</t>
@@ -701,7 +698,7 @@
     <t xml:space="preserve">0.41</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.09, 0.67]</t>
+    <t xml:space="preserve">[0.08, 0.66]</t>
   </si>
   <si>
     <t xml:space="preserve">0.88</t>
@@ -731,7 +728,7 @@
     <t xml:space="preserve">[0.02, 0.08]</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.01, 0.12]</t>
+    <t xml:space="preserve">[0.01, 0.11]</t>
   </si>
   <si>
     <t xml:space="preserve">0.21</t>
@@ -836,7 +833,7 @@
     <t xml:space="preserve">[0.02, 0.17]</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.02, 0.16]</t>
+    <t xml:space="preserve">[0.01, 0.16]</t>
   </si>
   <si>
     <t xml:space="preserve">[0.00, 0.16]</t>
@@ -854,9 +851,6 @@
     <t xml:space="preserve">[0.01, 0.15]</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.00, 0.17]</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.34</t>
   </si>
   <si>
@@ -873,9 +867,6 @@
   </si>
   <si>
     <t xml:space="preserve">[0.22, 0.67]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23</t>
   </si>
   <si>
     <t xml:space="preserve">[0.16, 0.33]</t>
@@ -1698,164 +1689,164 @@
         <v>63</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>82</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>54</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>87</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="I15" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="K15" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="I16" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1870,7 +1861,7 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1885,7 +1876,7 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1900,17 +1891,17 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1919,322 +1910,322 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>41</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>32</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>89</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="K24" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>79</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="J26" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>82</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="J28" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="K28" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>32</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>84</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2249,7 +2240,7 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2264,7 +2255,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2274,7 +2265,7 @@
         <v>32</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -2283,412 +2274,412 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="I34" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="J34" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="K34" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>82</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="K35" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>82</v>
       </c>
       <c r="G36" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="J36" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="K36" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="J37" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="H38" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="I38" s="1" t="s">
+      <c r="J38" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="K38" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>274</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>82</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="K39" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="I40" s="1" t="s">
+      <c r="K40" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="D42" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="I42" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="J42" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="K42" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>300</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>87</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>

--- a/Output/AllModels_SensitivityExchangeProcesses_12000.xlsx
+++ b/Output/AllModels_SensitivityExchangeProcesses_12000.xlsx
@@ -1,922 +1,929 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kueng\DataAnalysis\02TimeAndTiesControl\Output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBCACEF-EEF0-4359-8A88-EC20BED1FB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Subjective MVPA Hurdle Lognormal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device-Based MVPA Log (Gaussian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mood Gaussian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reactance Dichotome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hurdle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Zero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.)_hu pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI_hu pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.)_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.) pa_obj_log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI pa_obj_log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. mood_gauss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI mood_gauss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OR is_reactance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI is_reactance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intercept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.22***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.15,  0.32]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.99***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[28.75, 40.22]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.13***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[100.39, 123.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 3.47, 3.89]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.16,    0.68]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Within-Person Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.05,  1.41]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.94,  1.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.98,   1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.08, 0.01]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.72,    1.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.95,  1.27]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.96,  1.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.97,   1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.05, 0.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.89,    1.89]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.64,  1.34]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.81,  1.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.89,   1.02]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.15, 0.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.08,    5.47]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.07,  3.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.87,  1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.91,   1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.12, 0.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.48,    5.20]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.67,  1.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.90,  1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.95,   1.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.07, 0.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.06,    1.93]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.96,  1.57]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.90,  1.01]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.96,   1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.01, 0.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.57,    1.46]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.63,  1.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.87,  1.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.16, 0.36]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.61,    3.37]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Own action plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.03***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 8.87, 13.75]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.24,  1.50]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  1.01,   1.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.01, 0.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.48,    1.89]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner action plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.85,  1.30]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.95,  1.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.99,   1.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.10, 0.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.46,    1.62]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily support received</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.57,  1.90]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.05,  1.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  1.02,   1.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.06, 0.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.70,    0.99]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily support provided (partner's view)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.28,  1.53]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.02,  1.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  1.00,   1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.01, 0.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.71,    1.01]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is a Weekend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JITAI received</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days post skilled support intervention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily wear time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  1.00,   1.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Between-Person Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.52,  3.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.64,  1.35]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.76,   1.55]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.49, 1.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.43,   21.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.46,  2.68]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.62,  1.31]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.69,   1.45]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.40, 1.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.33,   23.75]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.03,  0.50]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.32,  1.80]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.61,   1.58]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.27, 0.64]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.75, 1156.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.07,  1.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.23,  1.35]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.61,   1.51]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.30, 0.62]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.06,  112.28]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.20,  3.37]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.73,  2.84]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.51,   1.58]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.94, 1.40]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.05,   62.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.36,  5.90]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.71,  2.81]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.63,   1.98]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.05, 1.29]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00,    1.73]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's received support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.94,  1.76]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.00,  1.30]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.94,   1.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.13, 0.44]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.18,    1.52]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's received support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.09,  2.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.84,  1.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.87,   1.15]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.37, 0.21]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.42,    2.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference study group 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference study group 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean wear time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Effects (Level 3 - Couple)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.53, 1.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.14, 0.38]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.04, 0.32]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.08, 0.66]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.07, 1.75]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.41]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.09, 0.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.55]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.42]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 0.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 0.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.19, 1.23]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.95]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.22]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.14]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.28]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.11, 2.66]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 1.38]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.26]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.06, 3.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.18, 0.99]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.17]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.73]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.15]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 1.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2:sd(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.22, 0.67]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.16, 0.33]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.22, 0.37]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.48, 0.79]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.60, 2.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional Parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.62, 0.67]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.53, 0.56]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.84, 0.88]</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="299">
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Subjective MVPA Hurdle Lognormal</t>
+  </si>
+  <si>
+    <t>Device-Based MVPA Log (Gaussian)</t>
+  </si>
+  <si>
+    <t>Mood Gaussian</t>
+  </si>
+  <si>
+    <t>Reactance Dichotome</t>
+  </si>
+  <si>
+    <t>Hurdle</t>
+  </si>
+  <si>
+    <t>Non-Zero</t>
+  </si>
+  <si>
+    <t>exp(Est.)_hu pa_sub</t>
+  </si>
+  <si>
+    <t>95% CI_hu pa_sub</t>
+  </si>
+  <si>
+    <t>exp(Est.)_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t>95% CI_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t>exp(Est.) pa_obj_log</t>
+  </si>
+  <si>
+    <t>95% CI pa_obj_log</t>
+  </si>
+  <si>
+    <t>Est. mood_gauss</t>
+  </si>
+  <si>
+    <t>95% CI mood_gauss</t>
+  </si>
+  <si>
+    <t>OR is_reactance</t>
+  </si>
+  <si>
+    <t>95% CI is_reactance</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>0.22***</t>
+  </si>
+  <si>
+    <t>[ 0.15,  0.32]</t>
+  </si>
+  <si>
+    <t>33.99***</t>
+  </si>
+  <si>
+    <t>[28.75, 40.22]</t>
+  </si>
+  <si>
+    <t>111.13***</t>
+  </si>
+  <si>
+    <t>[100.39, 123.07]</t>
+  </si>
+  <si>
+    <t>3.68***</t>
+  </si>
+  <si>
+    <t>[ 3.47, 3.89]</t>
+  </si>
+  <si>
+    <t>0.33**</t>
+  </si>
+  <si>
+    <t>[0.16,    0.68]</t>
+  </si>
+  <si>
+    <t>Within-Person Effects</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.21*</t>
+  </si>
+  <si>
+    <t>[ 1.05,  1.41]</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>[ 0.94,  1.06]</t>
+  </si>
+  <si>
+    <t>1.01</t>
+  </si>
+  <si>
+    <t>[  0.98,   1.04]</t>
+  </si>
+  <si>
+    <t>-0.04</t>
+  </si>
+  <si>
+    <t>[-0.08, 0.01]</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>[0.72,    1.12]</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.09</t>
+  </si>
+  <si>
+    <t>[ 0.95,  1.27]</t>
+  </si>
+  <si>
+    <t>[ 0.96,  1.05]</t>
+  </si>
+  <si>
+    <t>[  0.97,   1.04]</t>
+  </si>
+  <si>
+    <t>-0.01</t>
+  </si>
+  <si>
+    <t>[-0.05, 0.04]</t>
+  </si>
+  <si>
+    <t>1.26</t>
+  </si>
+  <si>
+    <t>[0.89,    1.89]</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced pressure</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>[ 0.64,  1.34]</t>
+  </si>
+  <si>
+    <t>0.90*</t>
+  </si>
+  <si>
+    <t>[ 0.81,  1.00]</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>[  0.89,   1.02]</t>
+  </si>
+  <si>
+    <t>[-0.15, 0.07]</t>
+  </si>
+  <si>
+    <t>2.11*</t>
+  </si>
+  <si>
+    <t>[1.08,    5.47]</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced pressure</t>
+  </si>
+  <si>
+    <t>1.68*</t>
+  </si>
+  <si>
+    <t>[ 1.07,  3.18]</t>
+  </si>
+  <si>
+    <t>[ 0.87,  1.04]</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>[  0.91,   1.04]</t>
+  </si>
+  <si>
+    <t>[-0.12, 0.09]</t>
+  </si>
+  <si>
+    <t>1.36</t>
+  </si>
+  <si>
+    <t>[0.48,    5.20]</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced pushing</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>[ 0.67,  1.24]</t>
+  </si>
+  <si>
+    <t>[ 0.90,  1.03]</t>
+  </si>
+  <si>
+    <t>[  0.95,   1.06]</t>
+  </si>
+  <si>
+    <t>[-0.07, 0.05]</t>
+  </si>
+  <si>
+    <t>1.41*</t>
+  </si>
+  <si>
+    <t>[1.06,    1.93]</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced pushing</t>
+  </si>
+  <si>
+    <t>1.21</t>
+  </si>
+  <si>
+    <t>[ 0.96,  1.57]</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>[ 0.90,  1.01]</t>
+  </si>
+  <si>
+    <t>[  0.96,   1.04]</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>[-0.01, 0.12]</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>[0.57,    1.46]</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>[ 0.63,  1.18]</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>[ 0.87,  1.10]</t>
+  </si>
+  <si>
+    <t>0.26***</t>
+  </si>
+  <si>
+    <t>[ 0.16, 0.36]</t>
+  </si>
+  <si>
+    <t>1.43</t>
+  </si>
+  <si>
+    <t>[0.61,    3.37]</t>
+  </si>
+  <si>
+    <t>Own action plan</t>
+  </si>
+  <si>
+    <t>11.03***</t>
+  </si>
+  <si>
+    <t>[ 8.87, 13.75]</t>
+  </si>
+  <si>
+    <t>1.36***</t>
+  </si>
+  <si>
+    <t>[ 1.24,  1.50]</t>
+  </si>
+  <si>
+    <t>1.06*</t>
+  </si>
+  <si>
+    <t>[  1.01,   1.11]</t>
+  </si>
+  <si>
+    <t>[-0.01, 0.13]</t>
+  </si>
+  <si>
+    <t>[0.48,    1.89]</t>
+  </si>
+  <si>
+    <t>Partner action plan</t>
+  </si>
+  <si>
+    <t>1.05</t>
+  </si>
+  <si>
+    <t>[ 0.85,  1.30]</t>
+  </si>
+  <si>
+    <t>1.04</t>
+  </si>
+  <si>
+    <t>[ 0.95,  1.13]</t>
+  </si>
+  <si>
+    <t>[  0.99,   1.09]</t>
+  </si>
+  <si>
+    <t>-0.03</t>
+  </si>
+  <si>
+    <t>[-0.10, 0.04]</t>
+  </si>
+  <si>
+    <t>[0.46,    1.62]</t>
+  </si>
+  <si>
+    <t>Daily support received</t>
+  </si>
+  <si>
+    <t>1.73***</t>
+  </si>
+  <si>
+    <t>[ 1.57,  1.90]</t>
+  </si>
+  <si>
+    <t>1.08***</t>
+  </si>
+  <si>
+    <t>[ 1.05,  1.10]</t>
+  </si>
+  <si>
+    <t>1.04***</t>
+  </si>
+  <si>
+    <t>[  1.02,   1.05]</t>
+  </si>
+  <si>
+    <t>0.08***</t>
+  </si>
+  <si>
+    <t>[ 0.06, 0.11]</t>
+  </si>
+  <si>
+    <t>0.83*</t>
+  </si>
+  <si>
+    <t>[0.70,    0.99]</t>
+  </si>
+  <si>
+    <t>Daily support provided (partner's view)</t>
+  </si>
+  <si>
+    <t>1.40***</t>
+  </si>
+  <si>
+    <t>[ 1.28,  1.53]</t>
+  </si>
+  <si>
+    <t>1.05***</t>
+  </si>
+  <si>
+    <t>[ 1.02,  1.07]</t>
+  </si>
+  <si>
+    <t>[  1.00,   1.03]</t>
+  </si>
+  <si>
+    <t>0.04**</t>
+  </si>
+  <si>
+    <t>[ 0.01, 0.06]</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>[0.71,    1.01]</t>
+  </si>
+  <si>
+    <t>Is a Weekend</t>
+  </si>
+  <si>
+    <t>JITAI received</t>
+  </si>
+  <si>
+    <t>Days post skilled support intervention</t>
+  </si>
+  <si>
+    <t>Daily wear time</t>
+  </si>
+  <si>
+    <t>1.00***</t>
+  </si>
+  <si>
+    <t>[  1.00,   1.00]</t>
+  </si>
+  <si>
+    <t>Between-Person Effects</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.29</t>
+  </si>
+  <si>
+    <t>[ 0.52,  3.10]</t>
+  </si>
+  <si>
+    <t>[ 0.64,  1.35]</t>
+  </si>
+  <si>
+    <t>[  0.76,   1.55]</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>[-0.49, 1.00]</t>
+  </si>
+  <si>
+    <t>2.79</t>
+  </si>
+  <si>
+    <t>[0.43,   21.09]</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.12</t>
+  </si>
+  <si>
+    <t>[ 0.46,  2.68]</t>
+  </si>
+  <si>
+    <t>[ 0.62,  1.31]</t>
+  </si>
+  <si>
+    <t>[  0.69,   1.45]</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>[-0.40, 1.11]</t>
+  </si>
+  <si>
+    <t>2.55</t>
+  </si>
+  <si>
+    <t>[0.33,   23.75]</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced pressure</t>
+  </si>
+  <si>
+    <t>0.14**</t>
+  </si>
+  <si>
+    <t>[ 0.03,  0.50]</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>[ 0.32,  1.80]</t>
+  </si>
+  <si>
+    <t>[  0.61,   1.58]</t>
+  </si>
+  <si>
+    <t>-0.32</t>
+  </si>
+  <si>
+    <t>[-1.27, 0.64]</t>
+  </si>
+  <si>
+    <t>25.64</t>
+  </si>
+  <si>
+    <t>[0.75, 1156.07]</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced pressure</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>[ 0.07,  1.12]</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>[ 0.23,  1.35]</t>
+  </si>
+  <si>
+    <t>[  0.61,   1.51]</t>
+  </si>
+  <si>
+    <t>-0.33</t>
+  </si>
+  <si>
+    <t>[-1.30, 0.62]</t>
+  </si>
+  <si>
+    <t>2.88</t>
+  </si>
+  <si>
+    <t>[0.06,  112.28]</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced pushing</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>[ 0.20,  3.37]</t>
+  </si>
+  <si>
+    <t>1.44</t>
+  </si>
+  <si>
+    <t>[ 0.73,  2.84]</t>
+  </si>
+  <si>
+    <t>[  0.51,   1.58]</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>[-0.94, 1.40]</t>
+  </si>
+  <si>
+    <t>1.65</t>
+  </si>
+  <si>
+    <t>[0.05,   62.05]</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced pushing</t>
+  </si>
+  <si>
+    <t>1.45</t>
+  </si>
+  <si>
+    <t>[ 0.36,  5.90]</t>
+  </si>
+  <si>
+    <t>1.42</t>
+  </si>
+  <si>
+    <t>[ 0.71,  2.81]</t>
+  </si>
+  <si>
+    <t>1.11</t>
+  </si>
+  <si>
+    <t>[  0.63,   1.98]</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>[-1.05, 1.29]</t>
+  </si>
+  <si>
+    <t>[0.00,    1.73]</t>
+  </si>
+  <si>
+    <t>Mean individual's received support</t>
+  </si>
+  <si>
+    <t>[ 0.94,  1.76]</t>
+  </si>
+  <si>
+    <t>1.14</t>
+  </si>
+  <si>
+    <t>[ 1.00,  1.30]</t>
+  </si>
+  <si>
+    <t>1.08</t>
+  </si>
+  <si>
+    <t>[  0.94,   1.24]</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>[-0.13, 0.44]</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>[0.18,    1.52]</t>
+  </si>
+  <si>
+    <t>Mean partner's received support</t>
+  </si>
+  <si>
+    <t>1.48*</t>
+  </si>
+  <si>
+    <t>[ 1.09,  2.03]</t>
+  </si>
+  <si>
+    <t>[ 0.84,  1.10]</t>
+  </si>
+  <si>
+    <t>[  0.87,   1.15]</t>
+  </si>
+  <si>
+    <t>-0.08</t>
+  </si>
+  <si>
+    <t>[-0.37, 0.21]</t>
+  </si>
+  <si>
+    <t>[0.42,    2.09]</t>
+  </si>
+  <si>
+    <t>Difference study group 2</t>
+  </si>
+  <si>
+    <t>Difference study group 3</t>
+  </si>
+  <si>
+    <t>Mean wear time</t>
+  </si>
+  <si>
+    <t>Random Effects (Level 3 - Couple)</t>
+  </si>
+  <si>
+    <t>L3:sd(Intercept)</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>[0.53, 1.09]</t>
+  </si>
+  <si>
+    <t>[0.14, 0.38]</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>[0.04, 0.32]</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>[0.08, 0.66]</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>[0.07, 1.75]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced persuasion)</t>
+  </si>
+  <si>
+    <t>0.18</t>
+  </si>
+  <si>
+    <t>[0.01, 0.41]</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>[0.09, 0.18]</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>[0.02, 0.08]</t>
+  </si>
+  <si>
+    <t>[0.01, 0.11]</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>[0.01, 0.55]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced persuasion)</t>
+  </si>
+  <si>
+    <t>0.19</t>
+  </si>
+  <si>
+    <t>[0.01, 0.42]</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>[0.03, 0.12]</t>
+  </si>
+  <si>
+    <t>[0.03, 0.09]</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>[0.02, 0.13]</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>[0.19, 1.23]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced pressure)</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>[0.01, 0.95]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.22]</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>[0.00, 0.14]</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>[0.00, 0.28]</t>
+  </si>
+  <si>
+    <t>[0.11, 2.66]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>[0.03, 1.38]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.18]</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>[0.00, 0.10]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.26]</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>[0.06, 3.16]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced pushing)</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>[0.18, 0.99]</t>
+  </si>
+  <si>
+    <t>[0.02, 0.17]</t>
+  </si>
+  <si>
+    <t>[0.01, 0.16]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.16]</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>[0.02, 0.73]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced pushing)</t>
+  </si>
+  <si>
+    <t>[0.01, 0.15]</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>[0.02, 1.24]</t>
+  </si>
+  <si>
+    <t>Random Effects (Level 2 - Couple:Person)</t>
+  </si>
+  <si>
+    <t>L2:sd(Intercept)</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>[0.22, 0.67]</t>
+  </si>
+  <si>
+    <t>[0.16, 0.33]</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>[0.22, 0.37]</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>[0.48, 0.79]</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>[0.60, 2.00]</t>
+  </si>
+  <si>
+    <t>Additional Parameters</t>
+  </si>
+  <si>
+    <t>sigma</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>[0.62, 0.67]</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>[0.53, 0.56]</t>
+  </si>
+  <si>
+    <t>[0.84, 0.88]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -930,24 +937,30 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <i/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -959,20 +972,28 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -985,20 +1006,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1280,46 +1322,59 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="41.140625" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1354,7 +1409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1389,7 +1444,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1424,43 +1479,43 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -1494,11 +1549,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="11" t="s">
         <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1529,8 +1584,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1564,8 +1619,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1599,11 +1654,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="12" t="s">
         <v>69</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1634,11 +1689,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="11" t="s">
         <v>77</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1656,7 +1711,7 @@
       <c r="G11" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="11" t="s">
         <v>82</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -1669,8 +1724,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>86</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1704,8 +1759,8 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>95</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -1739,8 +1794,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>104</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1774,8 +1829,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>113</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -1809,8 +1864,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>124</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -1844,8 +1899,8 @@
         <v>133</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>134</v>
       </c>
       <c r="B17" s="1"/>
@@ -1859,8 +1914,8 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>135</v>
       </c>
       <c r="B18" s="1"/>
@@ -1874,8 +1929,8 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>136</v>
       </c>
       <c r="B19" s="1"/>
@@ -1889,8 +1944,8 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>137</v>
       </c>
       <c r="B20" s="1"/>
@@ -1908,43 +1963,43 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" s="10" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>141</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1978,8 +2033,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>150</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -2013,8 +2068,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>159</v>
       </c>
       <c r="B24" s="5" t="s">
@@ -2048,8 +2103,8 @@
         <v>168</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>169</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -2083,8 +2138,8 @@
         <v>178</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>179</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -2118,8 +2173,8 @@
         <v>188</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>189</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -2153,8 +2208,8 @@
         <v>198</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>199</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -2188,8 +2243,8 @@
         <v>208</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>209</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -2223,8 +2278,8 @@
         <v>216</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>217</v>
       </c>
       <c r="B30" s="1"/>
@@ -2238,8 +2293,8 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>218</v>
       </c>
       <c r="B31" s="1"/>
@@ -2253,8 +2308,8 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>219</v>
       </c>
       <c r="B32" s="1"/>
@@ -2272,43 +2327,43 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="K33" s="10" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>221</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -2342,8 +2397,8 @@
         <v>230</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
         <v>231</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -2377,8 +2432,8 @@
         <v>240</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
         <v>241</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -2412,8 +2467,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
         <v>251</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -2447,8 +2502,8 @@
         <v>259</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
         <v>260</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -2482,8 +2537,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="s">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
         <v>269</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -2517,8 +2572,8 @@
         <v>276</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
         <v>277</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -2552,43 +2607,43 @@
         <v>280</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="s">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="J41" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="K41" s="10" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="s">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
         <v>282</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -2622,43 +2677,43 @@
         <v>291</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="6" t="s">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="K43" s="10" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="s">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
         <v>293</v>
       </c>
       <c r="B44" s="4"/>
@@ -2684,37 +2739,37 @@
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
     </row>
-    <row r="45">
-      <c r="A45" s="7"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7"/>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="6"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="6"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="6"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="6"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="6"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A43:K43"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A43:K43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Output/AllModels_SensitivityExchangeProcesses_12000.xlsx
+++ b/Output/AllModels_SensitivityExchangeProcesses_12000.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="301">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -722,24 +722,6 @@
     <t xml:space="preserve">[0.05, 1.63]</t>
   </si>
   <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pushing)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
   </si>
   <si>
@@ -771,6 +753,147 @@
   </si>
   <si>
     <t xml:space="preserve">[0.61, 2.29]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.06, 0.55]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.08, 0.17]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.08]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05, 0.75]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.10]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.13]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.14, 1.19]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 1.59]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.20]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.24]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.32, 3.25]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.04, 2.02]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.17]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.23]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.04, 3.43]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.13, 1.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.15]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.16]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.71]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.70]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.13]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.10]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.92]</t>
   </si>
   <si>
     <t xml:space="preserve">Additional Parameters</t>
@@ -855,7 +978,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -873,6 +996,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
@@ -2226,223 +2352,343 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
+      <c r="B35" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
+      <c r="B36" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
+        <v>247</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
+        <v>256</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
+        <v>263</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
+        <v>271</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="s">
-        <v>242</v>
+      <c r="A41" s="7" t="s">
+        <v>278</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>242</v>
+        <v>280</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>242</v>
+        <v>283</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>242</v>
+        <v>285</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>242</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>245</v>
+        <v>289</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>248</v>
+        <v>291</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>249</v>
+        <v>102</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>250</v>
+        <v>292</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="s">
-        <v>254</v>
+      <c r="A44" s="9" t="s">
+        <v>295</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>175</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
@@ -2474,7 +2720,7 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A21:K21"/>
     <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A35:K35"/>
     <mergeCell ref="A43:K43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
